--- a/Total_Mass_Calculations/Oxides.xlsx
+++ b/Total_Mass_Calculations/Oxides.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unibe365-my.sharepoint.com/personal/sebastian_stumpf_unibe_ch/Documents/PhD/ICP-Base/ICP-Base_dev/Total_Mass_Calculations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="11_AD4DB114E441178AC67DF4EAB656CEA0693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1671DFC7-5C35-4482-8AE9-DD5D7371C453}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="11_AD4DB114E441178AC67DF4EAB656CEA0693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD1E1C56-3D14-43D0-A70A-92DCF4B73D15}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="195" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="157">
   <si>
     <t>SiO2</t>
   </si>
@@ -442,6 +442,60 @@
   </si>
   <si>
     <t>Conversion_Factor</t>
+  </si>
+  <si>
+    <t>Preferred_Isotope</t>
+  </si>
+  <si>
+    <t>Ca43</t>
+  </si>
+  <si>
+    <t>Si29</t>
+  </si>
+  <si>
+    <t>Mg25</t>
+  </si>
+  <si>
+    <t>K39</t>
+  </si>
+  <si>
+    <t>Mo95</t>
+  </si>
+  <si>
+    <t>Br79</t>
+  </si>
+  <si>
+    <t>Al27</t>
+  </si>
+  <si>
+    <t>Na23</t>
+  </si>
+  <si>
+    <t>Ti49</t>
+  </si>
+  <si>
+    <t>Fe57</t>
+  </si>
+  <si>
+    <t>Ni61</t>
+  </si>
+  <si>
+    <t>Cr53</t>
+  </si>
+  <si>
+    <t>S34</t>
+  </si>
+  <si>
+    <t>Cl35</t>
+  </si>
+  <si>
+    <t>Major_Element</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -769,14 +823,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>136</v>
       </c>
@@ -786,8 +843,14 @@
       <c r="C1" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -797,8 +860,11 @@
       <c r="C2" s="1">
         <v>1.079</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -808,8 +874,14 @@
       <c r="C3" s="1">
         <v>1.889</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -819,8 +891,11 @@
       <c r="C4" s="1">
         <v>1.32</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -830,8 +905,11 @@
       <c r="C5" s="1">
         <v>1.2709999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E5" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -841,8 +919,11 @@
       <c r="C6" s="1">
         <v>3.22</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E6" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -852,8 +933,11 @@
       <c r="C7" s="1">
         <v>1.1160000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E7" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -863,8 +947,11 @@
       <c r="C8" s="1">
         <v>2.7850000000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E8" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -874,8 +961,11 @@
       <c r="C9" s="1">
         <v>1.159</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E9" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -885,8 +975,14 @@
       <c r="C10" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -896,8 +992,14 @@
       <c r="C11" s="1">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>140</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -907,8 +1009,11 @@
       <c r="C12" s="1">
         <v>1.143</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E12" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -918,8 +1023,11 @@
       <c r="C13" s="1">
         <v>1.357</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E13" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -929,8 +1037,14 @@
       <c r="C14" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -940,8 +1054,11 @@
       <c r="C15" s="1">
         <v>1.2709999999999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E15" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -951,8 +1068,14 @@
       <c r="C16" s="1">
         <v>1.462</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -962,8 +1085,11 @@
       <c r="C17" s="1">
         <v>1.0629999999999999</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E17" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -973,8 +1099,11 @@
       <c r="C18" s="1">
         <v>1.252</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E18" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
@@ -984,8 +1113,11 @@
       <c r="C19" s="1">
         <v>1.1479999999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E19" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
@@ -995,8 +1127,11 @@
       <c r="C20" s="1">
         <v>1.143</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E20" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
@@ -1006,8 +1141,11 @@
       <c r="C21" s="1">
         <v>1.1579999999999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E21" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -1017,8 +1155,14 @@
       <c r="C22" s="2">
         <v>1.286</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>149</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
@@ -1028,8 +1172,11 @@
       <c r="C23" s="1">
         <v>1.2849999999999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E23" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -1039,8 +1186,11 @@
       <c r="C24" s="1">
         <v>1.1519999999999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>35</v>
       </c>
@@ -1050,8 +1200,11 @@
       <c r="C25" s="1">
         <v>1.43</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E25" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
@@ -1061,8 +1214,11 @@
       <c r="C26" s="1">
         <v>1.2110000000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E26" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>37</v>
       </c>
@@ -1072,8 +1228,11 @@
       <c r="C27" s="1">
         <v>1.1459999999999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E27" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
@@ -1083,8 +1242,11 @@
       <c r="C28" s="1">
         <v>1.2030000000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>134</v>
       </c>
@@ -1094,8 +1256,11 @@
       <c r="C29" s="1">
         <v>1.1665000000000001</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E29" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -1105,8 +1270,14 @@
       <c r="C30" s="1">
         <v>1.204</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
@@ -1116,8 +1287,11 @@
       <c r="C31" s="1">
         <v>1.1719999999999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E31" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
@@ -1127,8 +1301,11 @@
       <c r="C32" s="1">
         <v>1.34</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
@@ -1138,8 +1315,11 @@
       <c r="C33" s="1">
         <v>1.137</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E33" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>43</v>
       </c>
@@ -1149,8 +1329,14 @@
       <c r="C34" s="1">
         <v>1.6579999999999999</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>45</v>
       </c>
@@ -1160,8 +1346,11 @@
       <c r="C35" s="2">
         <v>1.2909999999999999</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E35" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>46</v>
       </c>
@@ -1171,8 +1360,14 @@
       <c r="C36" s="1">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>47</v>
       </c>
@@ -1182,8 +1377,14 @@
       <c r="C37" s="1">
         <v>1.3480000000000001</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>147</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>48</v>
       </c>
@@ -1193,8 +1394,11 @@
       <c r="C38" s="1">
         <v>1.431</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E38" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>49</v>
       </c>
@@ -1204,8 +1408,11 @@
       <c r="C39" s="1">
         <v>1.1659999999999999</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E39" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>50</v>
       </c>
@@ -1215,8 +1422,14 @@
       <c r="C40" s="1">
         <v>1.2729999999999999</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>150</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>52</v>
       </c>
@@ -1226,8 +1439,11 @@
       <c r="C41" s="1">
         <v>2.2909999999999999</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E41" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>53</v>
       </c>
@@ -1237,8 +1453,11 @@
       <c r="C42" s="1">
         <v>1.077</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E42" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>55</v>
       </c>
@@ -1248,8 +1467,11 @@
       <c r="C43" s="1">
         <v>1.206</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E43" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>57</v>
       </c>
@@ -1259,8 +1481,11 @@
       <c r="C44" s="1">
         <v>1.208</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E44" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>58</v>
       </c>
@@ -1270,8 +1495,11 @@
       <c r="C45" s="1">
         <v>1.2130000000000001</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E45" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>59</v>
       </c>
@@ -1281,8 +1509,11 @@
       <c r="C46" s="1">
         <v>1.0920000000000001</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E46" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
@@ -1292,8 +1523,11 @@
       <c r="C47" s="1">
         <v>1.881</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E47" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>61</v>
       </c>
@@ -1303,8 +1537,11 @@
       <c r="C48" s="1">
         <v>1.3660000000000001</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E48" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>62</v>
       </c>
@@ -1314,8 +1551,14 @@
       <c r="C49" s="1">
         <v>2.4980000000000002</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>63</v>
       </c>
@@ -1325,8 +1568,11 @@
       <c r="C50" s="1">
         <v>1.53</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E50" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>64</v>
       </c>
@@ -1336,8 +1582,11 @@
       <c r="C51" s="1">
         <v>1.546</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E51" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>65</v>
       </c>
@@ -1347,8 +1596,11 @@
       <c r="C52" s="1">
         <v>1.3660000000000001</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E52" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>66</v>
       </c>
@@ -1358,8 +1610,14 @@
       <c r="C53" s="1">
         <v>2.1389999999999998</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>141</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>67</v>
       </c>
@@ -1369,8 +1627,11 @@
       <c r="C54" s="1">
         <v>1.1599999999999999</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E54" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>68</v>
       </c>
@@ -1380,8 +1641,11 @@
       <c r="C55" s="1">
         <v>1.2689999999999999</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E55" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>69</v>
       </c>
@@ -1391,8 +1655,11 @@
       <c r="C56" s="1">
         <v>1.1830000000000001</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E56" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>71</v>
       </c>
@@ -1402,8 +1669,11 @@
       <c r="C57" s="1">
         <v>1.2210000000000001</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E57" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>72</v>
       </c>
@@ -1413,8 +1683,11 @@
       <c r="C58" s="1">
         <v>1.1759999999999999</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E58" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>73</v>
       </c>
@@ -1424,8 +1697,11 @@
       <c r="C59" s="1">
         <v>1.2230000000000001</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E59" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>74</v>
       </c>
@@ -1435,8 +1711,11 @@
       <c r="C60" s="1">
         <v>1.137</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E60" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>75</v>
       </c>
@@ -1446,8 +1725,14 @@
       <c r="C61" s="1">
         <v>1.6679999999999999</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>148</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>76</v>
       </c>
@@ -1457,8 +1742,11 @@
       <c r="C62" s="1">
         <v>1.123</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E62" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>77</v>
       </c>
@@ -1468,8 +1756,11 @@
       <c r="C63" s="1">
         <v>1.1419999999999999</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E63" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>78</v>
       </c>
@@ -1479,8 +1770,11 @@
       <c r="C64" s="1">
         <v>1.1339999999999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E64" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>79</v>
       </c>
@@ -1490,8 +1784,11 @@
       <c r="C65" s="1">
         <v>1.7849999999999999</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E65" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>80</v>
       </c>
@@ -1501,8 +1798,11 @@
       <c r="C66" s="1">
         <v>1.2609999999999999</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E66" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>81</v>
       </c>
@@ -1512,8 +1812,11 @@
       <c r="C67" s="1">
         <v>1.2789999999999999</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E67" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>82</v>
       </c>
@@ -1523,8 +1826,11 @@
       <c r="C68" s="1">
         <v>1.139</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E68" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>83</v>
       </c>
@@ -1534,8 +1840,11 @@
       <c r="C69" s="1">
         <v>1.2450000000000001</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E69" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>85</v>
       </c>
@@ -1544,6 +1853,9 @@
       </c>
       <c r="C70" s="1">
         <v>1.35</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
